--- a/data/trans_orig/P05A03-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P05A03-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive la contaminación es elevada en 2007</t>
+          <t>Población según si en el barrio donde vive la contaminación es elevada en 2007 (tasa de respuesta: 99,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>216595</t>
+          <t>216707</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>239684</t>
+          <t>238689</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>197305</t>
+          <t>196497</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>221330</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>422310</t>
+          <t>419655</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>455341</t>
+          <t>454687</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,2%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25501</t>
+          <t>25105</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47681</t>
+          <t>46696</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27456</t>
+          <t>27847</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51133</t>
+          <t>50759</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>59994</t>
+          <t>59409</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>91366</t>
+          <t>93389</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8984</t>
+          <t>9591</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11068</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3143</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15928</t>
+          <t>16164</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>316190</t>
+          <t>314052</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>358307</t>
+          <t>355570</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>325111</t>
+          <t>324734</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>365819</t>
+          <t>367260</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>656350</t>
+          <t>656155</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>714703</t>
+          <t>712670</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>71,99%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>114207</t>
+          <t>114950</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>153946</t>
+          <t>155072</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>109164</t>
+          <t>108954</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>147781</t>
+          <t>149380</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>231193</t>
+          <t>232910</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>289193</t>
+          <t>287400</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,03%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>12463</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32373</t>
+          <t>30819</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16814</t>
+          <t>16761</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36954</t>
+          <t>36879</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33060</t>
+          <t>32609</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60961</t>
+          <t>60801</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>306426</t>
+          <t>307033</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316772</t>
+          <t>316889</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>322665</t>
+          <t>323200</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>333150</t>
+          <t>333272</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>634652</t>
+          <t>634411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>648272</t>
+          <t>648170</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10673</t>
+          <t>10753</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11177</t>
+          <t>10821</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16887</t>
+          <t>17529</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>4939</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>6807</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>294566</t>
+          <t>293558</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>320197</t>
+          <t>320105</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>313286</t>
+          <t>314964</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>340058</t>
+          <t>339563</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>617577</t>
+          <t>614172</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>653369</t>
+          <t>651805</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,71%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25551</t>
+          <t>25858</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48511</t>
+          <t>49657</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25177</t>
+          <t>24621</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49395</t>
+          <t>48072</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56141</t>
+          <t>56771</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>87998</t>
+          <t>90039</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20258</t>
+          <t>19389</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14820</t>
+          <t>14956</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11927</t>
+          <t>11208</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29592</t>
+          <t>28560</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>132132</t>
+          <t>131939</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>156302</t>
+          <t>156264</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>128396</t>
+          <t>128598</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>154626</t>
+          <t>155937</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>267230</t>
+          <t>266977</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>305096</t>
+          <t>304889</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,8%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28049</t>
+          <t>28213</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49917</t>
+          <t>49686</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>37129</t>
+          <t>36440</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>60681</t>
+          <t>61977</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>69568</t>
+          <t>70143</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>104053</t>
+          <t>103802</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,47%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11021</t>
+          <t>11892</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28882</t>
+          <t>28869</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>9338</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24939</t>
+          <t>25378</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24431</t>
+          <t>24013</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46382</t>
+          <t>46153</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>239862</t>
+          <t>238907</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>257993</t>
+          <t>258279</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>236388</t>
+          <t>236757</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>257604</t>
+          <t>256769</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>483733</t>
+          <t>481955</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>510389</t>
+          <t>510615</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,02%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12818</t>
+          <t>12532</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30949</t>
+          <t>31904</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19558</t>
+          <t>20285</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>40401</t>
+          <t>40299</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>38099</t>
+          <t>37409</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64406</t>
+          <t>65749</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -3239,97 +3239,97 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>1947</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5758</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>1023</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>5997</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>5150</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1023</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>6718</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>544072</t>
+          <t>543884</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>571066</t>
+          <t>571701</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>584043</t>
+          <t>582993</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>607338</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1135211</t>
+          <t>1133648</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1171817</t>
+          <t>1173238</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,89%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>34356</t>
+          <t>33959</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>59394</t>
+          <t>59039</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19865</t>
+          <t>19709</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>39821</t>
+          <t>41189</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>60807</t>
+          <t>59321</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>92191</t>
+          <t>93475</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16156</t>
+          <t>16216</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5887</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19149</t>
+          <t>20030</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>12099</t>
+          <t>12922</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>30756</t>
+          <t>32613</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>523413</t>
+          <t>520261</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>571737</t>
+          <t>567806</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>527720</t>
+          <t>529912</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>579845</t>
+          <t>580629</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1069636</t>
+          <t>1066817</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1137183</t>
+          <t>1135082</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,01%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>136769</t>
+          <t>140818</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>182361</t>
+          <t>185051</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>168254</t>
+          <t>167925</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>216510</t>
+          <t>217140</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>319276</t>
+          <t>322370</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>385019</t>
+          <t>386848</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>18386</t>
+          <t>18359</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>39447</t>
+          <t>39061</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>21198</t>
+          <t>20114</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>42867</t>
+          <t>43409</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>44998</t>
+          <t>44830</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>74686</t>
+          <t>74498</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2642423</t>
+          <t>2646875</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2726713</t>
+          <t>2730191</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2707237</t>
+          <t>2709781</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2801468</t>
+          <t>2799803</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5378735</t>
+          <t>5381129</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5504669</t>
+          <t>5509040</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,33%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>436667</t>
+          <t>436005</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>515588</t>
+          <t>513509</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>466910</t>
+          <t>466603</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>553420</t>
+          <t>550222</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>926341</t>
+          <t>917937</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1042746</t>
+          <t>1033918</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>72138</t>
+          <t>71632</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>109152</t>
+          <t>110735</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>76243</t>
+          <t>79545</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>118135</t>
+          <t>118849</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>161323</t>
+          <t>165470</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>214393</t>
+          <t>216873</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive la contaminación es elevada en 2012</t>
+          <t>Población según si en el barrio donde vive la contaminación es elevada en 2012 (tasa de respuesta: 98,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>235030</t>
+          <t>235029</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>259272</t>
+          <t>259213</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>213349</t>
+          <t>213263</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>239421</t>
+          <t>239692</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>458719</t>
+          <t>459435</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>494809</t>
+          <t>493208</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,91%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21546</t>
+          <t>21600</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43599</t>
+          <t>43236</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29385</t>
+          <t>29525</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55297</t>
+          <t>55138</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55762</t>
+          <t>55997</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88961</t>
+          <t>87966</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15245</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11573</t>
+          <t>11931</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>6764</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22029</t>
+          <t>22880</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>361982</t>
+          <t>362422</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>402175</t>
+          <t>403566</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>402750</t>
+          <t>401531</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>438683</t>
+          <t>438337</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>778119</t>
+          <t>777630</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>832668</t>
+          <t>832788</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,62%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76202</t>
+          <t>75565</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>114080</t>
+          <t>115181</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62468</t>
+          <t>62199</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>97113</t>
+          <t>96135</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>148208</t>
+          <t>150600</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>197970</t>
+          <t>199404</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16600</t>
+          <t>16560</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40168</t>
+          <t>40151</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9165</t>
+          <t>9131</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25505</t>
+          <t>24903</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29565</t>
+          <t>29922</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57687</t>
+          <t>57222</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>301535</t>
+          <t>301563</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316091</t>
+          <t>316078</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>303894</t>
+          <t>302541</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>324359</t>
+          <t>323523</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>611333</t>
+          <t>612243</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>635284</t>
+          <t>636383</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4842</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16925</t>
+          <t>17600</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12602</t>
+          <t>13433</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30593</t>
+          <t>31418</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21807</t>
+          <t>21080</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43618</t>
+          <t>42661</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>924</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>8447</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>991</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10717</t>
+          <t>11783</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14825</t>
+          <t>14662</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>319981</t>
+          <t>319030</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>342678</t>
+          <t>342667</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>309344</t>
+          <t>307870</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>337389</t>
+          <t>337036</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>637192</t>
+          <t>636811</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>676685</t>
+          <t>673927</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,16%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21255</t>
+          <t>21869</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42382</t>
+          <t>45419</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29461</t>
+          <t>29320</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53410</t>
+          <t>54036</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>53920</t>
+          <t>56062</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>87749</t>
+          <t>89972</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9256</t>
+          <t>9157</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8831</t>
+          <t>8591</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27860</t>
+          <t>25214</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>11971</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30387</t>
+          <t>31135</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>137982</t>
+          <t>138577</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>165799</t>
+          <t>165827</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>138442</t>
+          <t>138600</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>165591</t>
+          <t>166278</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>285380</t>
+          <t>284891</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>324505</t>
+          <t>324248</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,02%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32375</t>
+          <t>32167</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>55887</t>
+          <t>57132</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36018</t>
+          <t>35877</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>62158</t>
+          <t>61141</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>73654</t>
+          <t>74646</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>107332</t>
+          <t>109410</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,31%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9852</t>
+          <t>9959</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27728</t>
+          <t>26461</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11848</t>
+          <t>10998</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28607</t>
+          <t>28417</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25896</t>
+          <t>25433</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48115</t>
+          <t>49288</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>251447</t>
+          <t>251408</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>266179</t>
+          <t>265881</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>266140</t>
+          <t>265367</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>277018</t>
+          <t>276953</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>523169</t>
+          <t>523438</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>540666</t>
+          <t>540810</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>4988</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17221</t>
+          <t>17119</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9809</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23596</t>
+          <t>23096</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>9280</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,82 +7594,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1731</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>10497</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>3,76%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>5780</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>12896</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1731</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>8144</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>5780</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>12770</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>620597</t>
+          <t>621523</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>640935</t>
+          <t>642079</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>642150</t>
+          <t>641533</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>663959</t>
+          <t>665400</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1270374</t>
+          <t>1269376</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1301112</t>
+          <t>1301387</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12753</t>
+          <t>12142</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30911</t>
+          <t>30950</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20221</t>
+          <t>19298</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>40747</t>
+          <t>41306</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>36657</t>
+          <t>36514</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>65622</t>
+          <t>66848</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10477</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11464</t>
+          <t>17145</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3682</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16324</t>
+          <t>16587</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>639234</t>
+          <t>638054</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>680429</t>
+          <t>680197</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>677932</t>
+          <t>678326</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>718477</t>
+          <t>720120</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1329148</t>
+          <t>1329138</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1389069</t>
+          <t>1386228</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8355,7 +8355,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>83371</t>
+          <t>82723</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>121166</t>
+          <t>121371</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>87303</t>
+          <t>87112</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>126771</t>
+          <t>126970</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>180543</t>
+          <t>181061</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>237338</t>
+          <t>237629</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,94%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>7815</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>24231</t>
+          <t>24996</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>17303</t>
+          <t>17662</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>15444</t>
+          <t>15284</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>34218</t>
+          <t>35800</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2938863</t>
+          <t>2937924</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3021739</t>
+          <t>3019012</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3027798</t>
+          <t>3032703</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3110370</t>
+          <t>3111893</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5988779</t>
+          <t>5994458</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6101308</t>
+          <t>6105418</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,33%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>304976</t>
+          <t>302649</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>377476</t>
+          <t>376430</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>329938</t>
+          <t>325693</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>405077</t>
+          <t>400681</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>655334</t>
+          <t>659790</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>758307</t>
+          <t>763388</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>62208</t>
+          <t>61221</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>100482</t>
+          <t>99877</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>58869</t>
+          <t>58334</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>94623</t>
+          <t>94859</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>129674</t>
+          <t>128063</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>183104</t>
+          <t>180409</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive la contaminación es elevada en 2016</t>
+          <t>Población según si en el barrio donde vive la contaminación es elevada en 2016 (tasa de respuesta: 99,18%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>204041</t>
+          <t>202420</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>236084</t>
+          <t>232520</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>195544</t>
+          <t>196087</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>226050</t>
+          <t>226571</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>409798</t>
+          <t>408123</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>451997</t>
+          <t>452131</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,44%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40732</t>
+          <t>42554</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69134</t>
+          <t>68958</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44555</t>
+          <t>44099</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70399</t>
+          <t>71740</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>92879</t>
+          <t>93755</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131971</t>
+          <t>131191</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5777</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>20949</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7885</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23549</t>
+          <t>22856</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17146</t>
+          <t>16401</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38729</t>
+          <t>37899</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>315569</t>
+          <t>318834</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>362178</t>
+          <t>360543</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>333513</t>
+          <t>331521</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>377859</t>
+          <t>376103</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>663215</t>
+          <t>662340</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>725495</t>
+          <t>723534</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>70,9%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83194</t>
+          <t>83117</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>119273</t>
+          <t>117722</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>80176</t>
+          <t>81021</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>116686</t>
+          <t>116562</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>172370</t>
+          <t>171686</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>224065</t>
+          <t>222511</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46827</t>
+          <t>47427</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79261</t>
+          <t>78238</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50567</t>
+          <t>51303</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82710</t>
+          <t>83686</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>107177</t>
+          <t>106223</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>152486</t>
+          <t>151673</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>280753</t>
+          <t>281768</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>299946</t>
+          <t>300107</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>299109</t>
+          <t>299348</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>318276</t>
+          <t>318193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>586294</t>
+          <t>587835</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>613975</t>
+          <t>614958</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16817</t>
+          <t>17066</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35751</t>
+          <t>35258</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14698</t>
+          <t>14582</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33005</t>
+          <t>32255</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>34884</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63161</t>
+          <t>61417</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>901</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>992</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11102</t>
+          <t>12749</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>320699</t>
+          <t>321063</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>343059</t>
+          <t>342285</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>309563</t>
+          <t>308430</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>337454</t>
+          <t>337478</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>640196</t>
+          <t>637787</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>675089</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,39%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15975</t>
+          <t>16593</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35396</t>
+          <t>35928</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33695</t>
+          <t>33932</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59444</t>
+          <t>60233</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54041</t>
+          <t>54526</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>86591</t>
+          <t>87655</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15197</t>
+          <t>15339</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20246</t>
+          <t>19650</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>12190</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31124</t>
+          <t>30065</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>166646</t>
+          <t>166034</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>187654</t>
+          <t>187444</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>173553</t>
+          <t>173902</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>195177</t>
+          <t>194634</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>347748</t>
+          <t>346074</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>376057</t>
+          <t>376403</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,57%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22518</t>
+          <t>22762</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>43171</t>
+          <t>43517</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16900</t>
+          <t>17039</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>36173</t>
+          <t>35133</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>45039</t>
+          <t>44952</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>72574</t>
+          <t>72816</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15245</t>
+          <t>15366</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4447</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16800</t>
+          <t>15827</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>238671</t>
+          <t>239329</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>254488</t>
+          <t>254016</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>252027</t>
+          <t>251561</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>265908</t>
+          <t>265052</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>495355</t>
+          <t>496770</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>516181</t>
+          <t>516682</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8635</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24452</t>
+          <t>23794</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6172</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20053</t>
+          <t>20519</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19022</t>
+          <t>18521</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>39848</t>
+          <t>38433</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -11919,97 +11919,97 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>1942</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1969</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>497805</t>
+          <t>498667</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>540315</t>
+          <t>541680</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>515825</t>
+          <t>516196</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>560521</t>
+          <t>558971</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1030220</t>
+          <t>1028557</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1087563</t>
+          <t>1092596</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>82,05%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>88844</t>
+          <t>87254</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>130091</t>
+          <t>128619</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>92670</t>
+          <t>93792</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>132142</t>
+          <t>133475</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>193839</t>
+          <t>190280</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>246896</t>
+          <t>249528</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12241</t>
+          <t>12824</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>31196</t>
+          <t>30609</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>21320</t>
+          <t>22075</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>45032</t>
+          <t>45077</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>39109</t>
+          <t>39742</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>68711</t>
+          <t>68834</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>705742</t>
+          <t>706849</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>735123</t>
+          <t>735422</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>739232</t>
+          <t>738279</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>770681</t>
+          <t>772099</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1456817</t>
+          <t>1455019</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1499194</t>
+          <t>1498065</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>34001</t>
+          <t>33417</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>61652</t>
+          <t>60874</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>48637</t>
+          <t>46930</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>79167</t>
+          <t>80173</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>88667</t>
+          <t>89801</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>130610</t>
+          <t>133048</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12979</t>
+          <t>13368</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>13671</t>
+          <t>13992</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2810143</t>
+          <t>2806456</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2894074</t>
+          <t>2893237</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2899210</t>
+          <t>2894161</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2989091</t>
+          <t>2986248</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5731159</t>
+          <t>5726231</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5856322</t>
+          <t>5849735</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,02%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>368315</t>
+          <t>367523</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>446744</t>
+          <t>441768</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>393223</t>
+          <t>394783</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>473483</t>
+          <t>480150</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>783832</t>
+          <t>785637</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>895715</t>
+          <t>900310</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>90057</t>
+          <t>90441</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>133003</t>
+          <t>131766</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>113129</t>
+          <t>115479</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>159014</t>
+          <t>164123</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>213614</t>
+          <t>215007</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>278476</t>
+          <t>280469</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive la contaminación es elevada en 2023</t>
+          <t>Población según si en el barrio donde vive la contaminación es elevada en 2023 (tasa de respuesta: 99,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>297678</t>
+          <t>299239</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>309889</t>
+          <t>309978</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>275694</t>
+          <t>275351</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>285411</t>
+          <t>285578</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>579860</t>
+          <t>579629</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>594233</t>
+          <t>594082</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1554</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13765</t>
+          <t>12204</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13881,12 +13881,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4224</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13941</t>
+          <t>14284</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6995</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21217</t>
+          <t>21448</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -13979,97 +13979,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1032</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>1327</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>448432</t>
+          <t>447393</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>479375</t>
+          <t>478143</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>427724</t>
+          <t>425458</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>454065</t>
+          <t>453991</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>886167</t>
+          <t>885540</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>927607</t>
+          <t>926193</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,47%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28909</t>
+          <t>30319</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57929</t>
+          <t>58330</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44812</t>
+          <t>45638</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70629</t>
+          <t>71997</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>82098</t>
+          <t>82718</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>119797</t>
+          <t>121055</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12749</t>
+          <t>12400</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>7086</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18195</t>
+          <t>19147</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10940</t>
+          <t>10521</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25583</t>
+          <t>25007</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>273105</t>
+          <t>272803</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>295265</t>
+          <t>294896</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>302845</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>322178</t>
+          <t>323600</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>584900</t>
+          <t>583017</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>613312</t>
+          <t>612517</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,71%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25603</t>
+          <t>25096</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,12 +14793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13408</t>
+          <t>12828</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28583</t>
+          <t>29701</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24134</t>
+          <t>25727</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46518</t>
+          <t>48125</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>6891</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22007</t>
+          <t>22387</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7381</t>
+          <t>7599</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22132</t>
+          <t>20759</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17245</t>
+          <t>17253</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37757</t>
+          <t>37415</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>236931</t>
+          <t>235195</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>266997</t>
+          <t>266958</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>386332</t>
+          <t>386075</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>431819</t>
+          <t>431517</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>633606</t>
+          <t>633985</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>694024</t>
+          <t>697610</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>89,01%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39219</t>
+          <t>37996</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68105</t>
+          <t>68814</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31100</t>
+          <t>31132</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69275</t>
+          <t>70967</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74710</t>
+          <t>72864</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>126179</t>
+          <t>128705</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15522</t>
+          <t>14346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>7189</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22112</t>
+          <t>21772</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12004</t>
+          <t>11734</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30556</t>
+          <t>29460</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>155119</t>
+          <t>156814</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>168416</t>
+          <t>168780</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>235709</t>
+          <t>235489</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>249744</t>
+          <t>249708</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>395999</t>
+          <t>396074</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>416392</t>
+          <t>417545</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15662,12 +15662,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15690,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>9962</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23623</t>
+          <t>21928</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21257</t>
+          <t>21702</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19560</t>
+          <t>18477</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>40084</t>
+          <t>39763</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -15803,97 +15803,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1225</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2090</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>413</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2120</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>2331</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>249025</t>
+          <t>249481</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>261962</t>
+          <t>261988</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>233075</t>
+          <t>234087</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>246067</t>
+          <t>246132</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>486622</t>
+          <t>487682</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>504989</t>
+          <t>505536</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>6283</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18295</t>
+          <t>18760</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9132</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21570</t>
+          <t>20397</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18025</t>
+          <t>17293</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35266</t>
+          <t>34815</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>512</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5562</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>508</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16314,7 +16314,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>7644</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>514794</t>
+          <t>516496</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>554048</t>
+          <t>553699</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>738720</t>
+          <t>738483</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>812928</t>
+          <t>807250</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1265726</t>
+          <t>1268450</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1361982</t>
+          <t>1367580</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>33838</t>
+          <t>33048</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>63757</t>
+          <t>61538</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20380</t>
+          <t>22197</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>69423</t>
+          <t>69701</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>57515</t>
+          <t>56002</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>120807</t>
+          <t>120858</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,7 +16687,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21417</t>
+          <t>22061</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>52180</t>
+          <t>52842</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>11999</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>40068</t>
+          <t>40046</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,7 +16765,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>36327</t>
+          <t>36339</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>83497</t>
+          <t>82792</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16805,7 +16805,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>869584</t>
+          <t>868144</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>911436</t>
+          <t>911060</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>646873</t>
+          <t>647393</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>671378</t>
+          <t>672326</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1524881</t>
+          <t>1525419</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1586161</t>
+          <t>1583753</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,12 +17030,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>14690</t>
+          <t>14996</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>53240</t>
+          <t>53634</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>36491</t>
+          <t>35694</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>60711</t>
+          <t>59089</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>48623</t>
+          <t>49533</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>103278</t>
+          <t>102427</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>823</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10554</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13512</t>
+          <t>13049</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>19069</t>
+          <t>19332</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3111175</t>
+          <t>3114691</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3221765</t>
+          <t>3219126</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3312526</t>
+          <t>3314224</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3415724</t>
+          <t>3415645</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6452452</t>
+          <t>6452127</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6599474</t>
+          <t>6597699</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>174314</t>
+          <t>175934</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>259191</t>
+          <t>259850</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>214492</t>
+          <t>214691</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>297319</t>
+          <t>295560</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>416420</t>
+          <t>414946</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>531429</t>
+          <t>533341</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>46163</t>
+          <t>47579</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>88858</t>
+          <t>88356</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>57377</t>
+          <t>57999</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>91711</t>
+          <t>94586</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>111445</t>
+          <t>114284</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>167690</t>
+          <t>170204</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
